--- a/docs/reference/fba-prep-center/20260809_FBA納品代行業者_比較表.xlsx
+++ b/docs/reference/fba-prep-center/20260809_FBA納品代行業者_比較表.xlsx
@@ -548,95 +548,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="10" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>この表は 2026-08-26 に訂正されています</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>出典: Genspark AI Sheets が 2026-08-09 に生成した比較表（社長共有）。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>2026-08-21 の公式サイト裏取り（T-20260821-010・サトル）で、公式と食い違う記載が9件見つかりました。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>実在する企業についての誤った料金情報を公開し続けることになるため、社長ご判断「訂正して。」（2026-08-26）を受け、</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>誤りと確認できた値を削除し「【未確認】」に置き換えました（T-20260826-001・マリエ）。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>削除のみで、推測による書き換えはしていません。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>公式で確認済みの正しい値は下記にあります:</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">  workspace/output/deliverables/T-20260821-010/01_公式裏取りファクトシート.md （§4-1）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>訂正の一覧と根拠は docs/reference/fba-prep-center/README.md を参照してください。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>この表の値をそのまま判断に使わないでください。正しい値が必要な場合はリサーチャー（サトル）による</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>公式サイトの再取得が必要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-29〜30 再調査（T-20260929-001・サトル）：【未確認】にしていた箇所を各社公式サイトの現在値で埋めました。びーぷらすの荷受確認は2026-08-24に10円→30円へ改定されていたため修正。新規5社を含む最新の比較は workspace/output/deliverables/T-20260929-001/01_FBA納品代行_公式値ファクトシート.md を参照してください。</t>
         </is>
       </c>
     </row>
@@ -712,7 +719,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ラベル貼り10円/個、荷受確認10円/SKU、納品代行手数料300円/箱（〜15kg）・400円/箱（〜25kg）、納品プラン作成10円/SKU、商品登録50円/SKU</t>
+          <t>ラベル貼り10円/個、荷受確認30円/SKU（2026-08-24改定・旧10円）、納品代行手数料300円/箱（〜15kg）・400円/箱（〜25kg）、納品プラン作成10円/SKU、商品登録50円/SKU、物価対応調整金5%（全額に加算）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -727,7 +734,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（「月間2万点以上の実績」は公式サイトに該当記述が無いため2026-08-26削除）セット組40〜50円、詳細検品20円、簡易検品無料。リサイクル段ボール無料。ChatWork＋Googleスプレッドシートで運用</t>
+          <t>セット組40〜50円、詳細検品20円、簡易検品無料。リサイクル段ボール無料。ChatWork＋Googleスプレッドシートで運用（「月間2万点以上の実績」は公式に記載なし）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="G2" s="4">
@@ -789,7 +796,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（「なし」は誤りのため2026-08-26削除。公式では保管パレットが荷受に必須と明記。登録初月無料・月500点以上で1枚目無料は公式と一致）</t>
+          <t>パレット保管3,000円/月（荷受に必須と公式明記・契約初月1パレット無料・月500点以上で1枚目無料）＋任意プランA500/B1,500/C5,000円/月。初期費用は公式に記載なし〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -799,7 +806,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>セラーセントラル権限付与で納品プラン作成まで代行。【未確認】（納品日数は公式FAQの記載と食い違うため2026-08-26削除）</t>
+          <t>セラーセントラル権限付与（4権限）で納品プラン作成まで代行。納品目安は公式内で表記ゆれ（本文「荷受けから2営業日以内」／FAQ「2〜3営業日以内」）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="G4" s="4">
@@ -825,7 +832,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（「なし」は誤りのため2026-08-26削除。公式には預託が必要な旨の記載あり）</t>
+          <t>月額・登録料なし。保証金50,000円（取引終了時に全額返還）。滞留在庫が多い場合はスペース使用料2,000円/月〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -856,12 +863,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>要見積</t>
+          <t>見積制（公式の料金PDFは「表示確認用サンプル」と明示）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>月額固定費・登録料なし。最低利用数量・期間の縛りなし（公式FAQ）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -875,7 +882,7 @@
         </is>
       </c>
       <c r="G6" s="4">
-        <f>HYPERLINK("https://joy-step.jp/request/","https://joy-step.jp/request/")</f>
+        <f>HYPERLINK("https://www.hakata-b-logi.jp/guide/","https://www.hakata-b-logi.jp/guide/")</f>
         <v/>
       </c>
     </row>
@@ -951,12 +958,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1点40円〜、送料45円〜</t>
+          <t>単品40円/点（検品・シール貼り含む）、セット80円、要期限・危険物+10円、大型100円。配送料（参考・税別・西濃）60サイズ45円〜／100サイズ200円〜／140サイズ550円〜〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>月額2,000円（全ユーザー）＋代行手数料が月5,000円未満の場合+3,000円（公式料金表の表記）。保管料は原則無料・30日間無料。初期費用は公式に記載なし〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -977,12 +984,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1個75円〜、FBA/RSL納品690円</t>
+          <t>公式掲載は保管料4.5円/1,000cm³/月、ネコポス290円、60サイズ590円、80サイズ680円、FBA/RSL納品690円（単位の記載なし）のみ。他は見積制〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>初期2,020円・月額2,020円（税込）のプランあり（無料プランの情報もあり）</t>
+          <t>公式に月額・初期費の記載なし（「初期2,020円・月額2,020円」は公式で確認できず）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1003,23 +1010,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（公式に料金表があるため「要見積」は誤り。2026-08-26削除）</t>
+          <t>FBA代行手数料100円/点（納品プラン作成・入荷・検品・ラベル出力/貼付・ピッキング・梱包込み）、同梱物封入10円/枚、セット組30円/セット〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（同上。2026-08-26削除）</t>
+          <t>月額5,000円。初期費用は公式に記載なし〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>通販事業者向け物流の実績豊富な会社。【未確認】（「大規模運用向き」は公式に該当記述が無いため2026-08-26削除）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>【出典不適切】第三者の一括見積りアグリゲータであり同社の公式サイトではないため2026-08-26削除</t>
-        </is>
+          <t>福岡市中央区。中古不可・温度管理品不可。出荷指示から中2〜3営業日（「大規模運用向き」は公式に記載なし）〔公式・2026-09-29取得／T-20260929-001〕</t>
+        </is>
+      </c>
+      <c r="E4" s="4">
+        <f>HYPERLINK("https://unistock.co.jp/fba_deliveryagency/","https://unistock.co.jp/fba_deliveryagency/")</f>
+        <v/>
       </c>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="10">
@@ -1030,23 +1036,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（ラベル貼り・セット梱包・配送料の3項目とも公式と食い違うため2026-08-26削除）</t>
+          <t>新品通常100円/点・大型200円/点（一般会員・税抜。検品・値札剥がし・クリーニング・出品登録/納品プラン作成・ラベル貼り・FC発送手配込み）、荷受50円/箱、セット梱包 小200円/大400円。FC送料 関東620〜2,280円／東海関西870〜2,810円／九州1,120〜4,650円（〜100〜200サイズ）、パートナーキャリア利用時+200円〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>【未確認】（公式に明記があるため「要確認」は不正確。2026-08-26削除）</t>
+          <t>一般会員 無料／プレミアム会員4,900円/月。大口契約のみ利用可（小口不可）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>中古品対応可</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>【出典不適切】別会社のブログ記事であり同社の公式サイトではないため2026-08-26削除</t>
-        </is>
+          <t>埼玉。中古品対応可。納品書・領収書の返送500円/回〔公式・2026-09-29取得／T-20260929-001〕</t>
+        </is>
+      </c>
+      <c r="E5" s="4">
+        <f>HYPERLINK("https://amazon-fbadaikou.jp/price/","https://amazon-fbadaikou.jp/price/")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1129,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>【未確認】（「ほぼ無料」は過度な一般化のため2026-08-26削除。就労支援系にも固定費が必要な事業者があります）</t>
+          <t>事業者ごとに異なる。びーぷらす・おりおん・Hakata B-Logi＝月額なし／糸星＝パレット3,000円/月が荷受に必須／タイシン＝月額なしだが保証金5万円（返還）〔公式・2026-09-29取得／T-20260929-001〕</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
